--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_lstm_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_lstm_quarterly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,27 +918,27 @@
         <v>1.134488500619101</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1040,35 +1041,35 @@
         <v>0.798509113087996</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1076,15 +1077,15 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1189,51 +1190,51 @@
         <v>0.8946626181871848</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1342,59 +1343,59 @@
         <v>0.7985091130879967</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AP6" s="3" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AR6" s="3" t="n">
@@ -1402,15 +1403,15 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AT6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
     </row>
@@ -1509,51 +1510,51 @@
         <v>1.205452781738563</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1662,59 +1663,59 @@
         <v>0.9173675959023833</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AP8" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AR8" s="3" t="n">
@@ -1722,15 +1723,15 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AT8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -1829,51 +1830,51 @@
         <v>0.4772531993303402</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -1982,59 +1983,59 @@
         <v>0.8498689068548888</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH10" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP10" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AR10" s="3" t="n">
@@ -2042,15 +2043,15 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AT10" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
     </row>
@@ -2349,66 +2350,68 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="M2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.4859401977791229</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="P2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.265757517207872</v>
+        <v>0.09032004823014436</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.265757517207872</v>
+        <v>0.04076898034342898</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>-0.03939252582908825</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.4859401977791229</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.9452989626493455</v>
+        <v>0.2044255219913531</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -2456,34 +2459,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>38835</v>
+        <v>36101</v>
       </c>
       <c r="M3" t="n">
-        <v>1532</v>
+        <v>75</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.3962590803105493</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.4021145509405996</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="P3" t="n">
-        <v>1524</v>
+        <v>73</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.1618137843831609</v>
+        <v>0.085146335583779</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.1454631295619674</v>
+        <v>0.0359218603967827</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -2493,29 +2496,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3962590803105493</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.4021145509405996</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>894</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-11</v>
+      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.6563396108953079</v>
+        <v>0.1967066132355302</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -2571,34 +2576,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>38012</v>
+        <v>36104</v>
       </c>
       <c r="M4" t="n">
-        <v>963</v>
+        <v>78</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2928258101948606</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="P4" t="n">
-        <v>813</v>
+        <v>77</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1378626392028849</v>
+        <v>0.08652899115469197</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.0982768979428859</v>
+        <v>0.03721870417281659</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -2608,38 +2613,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X4" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2928258101948606</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>380</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4140787579868381</v>
+        <v>0.1932346188529419</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.04718623161908146</v>
+        <v>0.001296843776033882</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.1034332701156887</v>
+        <v>0.002431450754154629</v>
       </c>
       <c r="AH4" t="n">
-        <v>-514</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -2694,34 +2701,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>36880</v>
+        <v>36038</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>38679</v>
+        <v>36480</v>
       </c>
       <c r="M5" t="n">
-        <v>1426</v>
+        <v>337</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1220322164304818</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1305473168703624</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="P5" t="n">
-        <v>1418</v>
+        <v>335</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.0766042964801181</v>
+        <v>0.1021175538718245</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.0664402793155538</v>
+        <v>0.09085415965367805</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -2731,38 +2738,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>189</v>
+        <v>31</v>
       </c>
       <c r="X5" t="n">
-        <v>-449</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1220322164304818</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1305473168703624</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1237</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>306</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>251</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.1389939570838696</v>
+        <v>0.1967066132355302</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.07902285024641356</v>
+        <v>0.05493229925689534</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.2742268638800676</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>343</v>
+        <v>262</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -2821,34 +2830,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>38947</v>
+        <v>36101</v>
       </c>
       <c r="M6" t="n">
-        <v>1610</v>
+        <v>75</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.3700926086423921</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.3762018586691143</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="P6" t="n">
-        <v>1602</v>
+        <v>73</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1575282730411565</v>
+        <v>0.08396785660670227</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.1451685759873488</v>
+        <v>0.03542467919685378</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -2858,50 +2867,52 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X6" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3700926086423921</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3762018586691143</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1027</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-11</v>
+      </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.5875349515184289</v>
+        <v>0.1967066132355302</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.0002945535746185224</v>
+        <v>-0.00049718119992892</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.02616647166815722</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.04689167804446294</v>
+        <v>-0.001794024975962802</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.07726679844753148</v>
+        <v>-0.002431450754154629</v>
       </c>
       <c r="AL6" t="n">
-        <v>647</v>
+        <v>-3</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -2952,76 +2963,80 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37691</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>36259</v>
+      </c>
       <c r="M7" t="n">
-        <v>1896</v>
+        <v>183</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.5421377227822665</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.546578367816291</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="P7" t="n">
-        <v>1889</v>
+        <v>181</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.326236951340748</v>
+        <v>0.09754917556589791</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.326236951340748</v>
+        <v>0.06403517154648716</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>-0.1162119622000858</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>742</v>
+        <v>31</v>
       </c>
       <c r="X7" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.5421377227822665</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.546578367816291</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1154</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>152</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>97</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>1.184062871649189</v>
+        <v>0.1967066132355302</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.1807738217787806</v>
+        <v>0.02811331114970446</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>-0.1458786424717171</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>108</v>
+      </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -3077,34 +3092,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>39094</v>
+        <v>36101</v>
       </c>
       <c r="M8" t="n">
-        <v>1710</v>
+        <v>75</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.4471675687328562</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.4525292958562871</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="P8" t="n">
-        <v>1702</v>
+        <v>73</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.2256672134076919</v>
+        <v>0.08396785660670227</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.2143185712972698</v>
+        <v>0.03542467919685378</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -3114,50 +3129,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.4471675687328562</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.4525292958562871</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1072</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-11</v>
+      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.8088663823645552</v>
+        <v>0.1967066132355302</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.06885544173530242</v>
+        <v>-0.00049718119992892</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>-0.05090848842230689</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.1160416733543839</v>
+        <v>-0.001794024975962802</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.1543417585379956</v>
+        <v>-0.002431450754154629</v>
       </c>
       <c r="AL8" t="n">
-        <v>692</v>
+        <v>-3</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -3208,75 +3225,73 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>37438</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>39065</v>
-      </c>
+        <v>35993</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>1692</v>
+        <v>90</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.2918668961380679</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.3230679747701246</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1578</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.2038631954324827</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.1925899590596433</v>
+        <v>0</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>568</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-70</v>
+        <v>-31</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.2918668961380679</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3230679747701246</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1124</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-55</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.4121638919947661</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.04712682949767596</v>
+        <v>-0.0359218603967827</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.1043921841724814</v>
+        <v>0.164373298400763</v>
       </c>
       <c r="AH9" t="n">
-        <v>230</v>
+        <v>-44</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -3285,8 +3300,12 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.05125509861622679</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.04687658655894855</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3335,34 +3354,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>38994</v>
+        <v>36104</v>
       </c>
       <c r="M10" t="n">
-        <v>1642</v>
+        <v>78</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.4256761935321316</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.440783672775422</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="P10" t="n">
-        <v>1596</v>
+        <v>77</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.1964515036714284</v>
+        <v>0.08652899115469197</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.182827059185811</v>
+        <v>0.03721870417281659</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -3372,56 +3391,62 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X10" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.4256761935321316</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.440783672775422</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1059</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.7411780405727388</v>
+        <v>0.1932346188529419</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.03736392962384369</v>
+        <v>0.001296843776033882</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>-0.02941711322158225</v>
+        <v>0.002431450754154629</v>
       </c>
       <c r="AH10" t="n">
-        <v>165</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.08455016124292515</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.1328503833372709</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>679</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="n">
+        <v>0.05125509861622679</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>-0.01065023267654031</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3718,68 +3743,66 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.4862309442441406</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.4862309442441406</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.2658275917027504</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.2658275917027504</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.5035092528573126</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.5040024023286764</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.2354171526922728</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1562892258388244</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>-0.03993583465459472</v>
+      </c>
       <c r="W2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.5035092528573126</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>860</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>1.014136226616542</v>
+        <v>0.94639982458421</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -3827,34 +3850,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>38835</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1531</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3956369736729513</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.4021145509405994</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1522</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1618665849188475</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.1455014831147333</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>41135</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1222</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.5315036835710506</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.5315036835710506</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1221</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.2301302896387797</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.153218484488933</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -3864,31 +3887,29 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.5315036835710506</v>
+        <v>-0.3956369736729513</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.5315036835710506</v>
+        <v>-0.4021145509405994</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>867</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7</v>
-      </c>
+        <v>894</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1.134488500619101</v>
+        <v>0.6546346424886254</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -3944,34 +3965,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>38007</v>
+      </c>
+      <c r="M4" t="n">
+        <v>959</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.291230325563591</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.3309499985899496</v>
+      </c>
+      <c r="P4" t="n">
+        <v>796</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1381187240689723</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.09828087349740594</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>40746</v>
-      </c>
-      <c r="M4" t="n">
-        <v>954</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
-      <c r="P4" t="n">
-        <v>953</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1982156637126214</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.1166175213781546</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -3981,40 +4002,38 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.291230325563591</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>599</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-261</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.798509113087996</v>
+        <v>0.410895578729674</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.03660096311077837</v>
+        <v>-0.04722060961732735</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.08751977085293516</v>
+        <v>0.1044066481093603</v>
       </c>
       <c r="AH4" t="n">
-        <v>-268</v>
+        <v>-517</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4069,34 +4088,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>36880</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>38679</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1425</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1211275409845358</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1305473168703624</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1416</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.07663114677613563</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.0664577939720363</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>41061</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>41401</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1403</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.2076096169385263</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.2466901429950641</v>
-      </c>
-      <c r="P5" t="n">
-        <v>467</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.09633155404230445</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.06871891125243719</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -4106,40 +4125,38 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1171</v>
+        <v>188</v>
       </c>
       <c r="X5" t="n">
-        <v>816</v>
+        <v>-449</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2076096169385263</v>
+        <v>-0.1211275409845358</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2466901429950641</v>
+        <v>-0.1305473168703624</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>232</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-628</v>
-      </c>
+        <v>1237</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2620042107734919</v>
+        <v>0.1378215231823581</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.08449957323649583</v>
+        <v>-0.07904368914269699</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3238940666325243</v>
+        <v>0.2745094326884154</v>
       </c>
       <c r="AH5" t="n">
-        <v>-635</v>
+        <v>343</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -4148,12 +4165,8 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.1280357344784944</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.09250707423188109</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4202,34 +4215,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>38947</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1609</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3694435395525626</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3762018586691142</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1575771851826235</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.1452068518688273</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>41117</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1210</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1209</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1828975982396791</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.1211725434075338</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -4239,62 +4252,56 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3694435395525626</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3762018586691142</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>855</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-5</v>
-      </c>
+        <v>1027</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.798509113087996</v>
+        <v>0.5859008078204586</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.03204594108139924</v>
+        <v>-0.0002946312459060352</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.08751977085293516</v>
+        <v>0.02619343412038866</v>
       </c>
       <c r="AH6" t="n">
-        <v>-12</v>
+        <v>133</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.00455502202937913</v>
+        <v>0.04692597837142132</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>0</v>
+        <v>-0.07821321398897163</v>
       </c>
       <c r="AL6" t="n">
-        <v>256</v>
+        <v>650</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.1280357344784944</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.003416596729815757</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4339,80 +4346,76 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>37691</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.5416659323959043</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.546578367816291</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1887</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.32632297209475</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.32632297209475</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>40133</v>
-      </c>
-      <c r="M7" t="n">
-        <v>531</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.314556771252366</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.314556771252366</v>
-      </c>
-      <c r="P7" t="n">
-        <v>530</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1125096100387912</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.04940485003028601</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>-0.1153012894485554</v>
+      </c>
       <c r="W7" t="n">
-        <v>355</v>
+        <v>741</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.314556771252366</v>
+        <v>-0.5416659323959043</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.314556771252366</v>
+        <v>-0.546578367816291</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>176</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-684</v>
-      </c>
+        <v>1154</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4589100279349019</v>
+        <v>1.181814686452219</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.103813634458647</v>
+        <v>0.1808214889800167</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2169469123186846</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-691</v>
-      </c>
+        <v>-0.1460289587229531</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -4468,34 +4471,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>39094</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1709</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.4465979192130793</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.4525292958562871</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1700</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.2257331869564692</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.2143750811540195</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>41158</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1238</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.4784516009673341</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.4784516009673341</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1237</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1962136257024649</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.1314888617422492</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -4505,52 +4508,50 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.4784516009673341</v>
+        <v>-0.4465979192130793</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.4784516009673341</v>
+        <v>-0.4525292958562871</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>883</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>23</v>
-      </c>
+        <v>1072</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.9173675959023841</v>
+        <v>0.8070044091233464</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.02172962274668383</v>
+        <v>0.06887359803928622</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.05305208260371652</v>
+        <v>-0.05096094554012809</v>
       </c>
       <c r="AH8" t="n">
-        <v>16</v>
+        <v>178</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.01487134036409454</v>
+        <v>0.1160942076566136</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.03446768824921864</v>
+        <v>-0.1553675936494884</v>
       </c>
       <c r="AL8" t="n">
-        <v>284</v>
+        <v>695</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -4601,34 +4602,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>37438</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>39064</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1690</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.2911372217200378</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.3230679747701248</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1570</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.2039819123926206</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.1926390360496827</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>40911</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>41366</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1378</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.1735482952034543</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.2236726154223472</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1242</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1100632696760414</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.07781237895827886</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -4638,40 +4639,38 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>1067</v>
+        <v>567</v>
       </c>
       <c r="X9" t="n">
-        <v>712</v>
+        <v>-70</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1735482952034543</v>
+        <v>-0.2911372217200378</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.2236726154223472</v>
+        <v>-0.3230679747701248</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>311</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-549</v>
-      </c>
+        <v>1123</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.2099920590594921</v>
+        <v>0.4107102681092594</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.07540610553065416</v>
+        <v>0.04713755293494937</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.3579553883675963</v>
+        <v>0.1044997519529135</v>
       </c>
       <c r="AH9" t="n">
-        <v>-556</v>
+        <v>229</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -4730,34 +4729,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>38988</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1637</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.4250843988723989</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.440783672775422</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1589</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.1967466700741274</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.1828711402733044</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>41117</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1210</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.4594211534155789</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4594211534155789</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1209</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.2055360906551242</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.1361709016762785</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -4767,52 +4766,50 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.4594211534155789</v>
+        <v>-0.4250843988723989</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.4594211534155789</v>
+        <v>-0.440783672775422</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>855</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-5</v>
-      </c>
+        <v>1055</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.8498689068548893</v>
+        <v>0.7393857429484723</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.01704758281265453</v>
+        <v>0.0373696571585711</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.07208253015547172</v>
+        <v>-0.02944742519944765</v>
       </c>
       <c r="AH10" t="n">
-        <v>-12</v>
+        <v>161</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.01955338029812384</v>
+        <v>0.08459026677589845</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.01543724069746344</v>
+        <v>-0.1338540733088079</v>
       </c>
       <c r="AL10" t="n">
-        <v>256</v>
+        <v>678</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -5115,34 +5112,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="M2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="P2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.08269444253856398</v>
+        <v>0.2354171526922728</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.05218963375687868</v>
+        <v>0.1563175570682493</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -5152,22 +5149,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -5176,7 +5173,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2429105460160748</v>
+        <v>1.014136226616542</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -5224,34 +5221,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>43521</v>
+        <v>41135</v>
       </c>
       <c r="M3" t="n">
-        <v>105</v>
+        <v>1222</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="P3" t="n">
-        <v>104</v>
+        <v>1221</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.05080546557820764</v>
+        <v>0.2301302896387797</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.02780108446333929</v>
+        <v>0.1532462590716843</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -5261,31 +5258,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>41</v>
+        <v>867</v>
       </c>
       <c r="AC3" t="n">
-        <v>-35</v>
+        <v>7</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.1801780858076512</v>
+        <v>1.134488500619101</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -5341,34 +5338,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43542</v>
+        <v>40746</v>
       </c>
       <c r="M4" t="n">
-        <v>120</v>
+        <v>954</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="P4" t="n">
-        <v>116</v>
+        <v>953</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04694464568316091</v>
+        <v>0.1982156637126214</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.02744587744229462</v>
+        <v>0.1166386611447342</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -5378,40 +5375,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>56</v>
+        <v>599</v>
       </c>
       <c r="AC4" t="n">
-        <v>-20</v>
+        <v>-261</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1600183179571426</v>
+        <v>0.798509113087996</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.0003552070210446692</v>
+        <v>-0.03660759792695012</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.01472560454206084</v>
+        <v>0.08751977085293516</v>
       </c>
       <c r="AH4" t="n">
-        <v>15</v>
+        <v>-268</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -5466,34 +5463,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>43458</v>
+        <v>41061</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43511</v>
+        <v>41401</v>
       </c>
       <c r="M5" t="n">
-        <v>100</v>
+        <v>1403</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1476887982658786</v>
+        <v>-0.2076096169385263</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1513122874756199</v>
+        <v>-0.2466901429950641</v>
       </c>
       <c r="P5" t="n">
-        <v>87</v>
+        <v>467</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.05083098220090135</v>
+        <v>0.09633155404230445</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.02715110801405351</v>
+        <v>0.06873136822911025</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -5503,40 +5500,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>64</v>
+        <v>1171</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1476887982658786</v>
+        <v>-0.2076096169385263</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1513122874756199</v>
+        <v>-0.2466901429950641</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>36</v>
+        <v>232</v>
       </c>
       <c r="AC5" t="n">
-        <v>-40</v>
+        <v>-628</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.1732803675058938</v>
+        <v>0.2620042107734919</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.0006499764492857822</v>
+        <v>-0.08451489084257408</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.004981453770149358</v>
+        <v>0.3238940666325243</v>
       </c>
       <c r="AH5" t="n">
-        <v>-5</v>
+        <v>-635</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -5546,10 +5543,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.1461547765376521</v>
+        <v>0.1280357344784944</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.1193965406079239</v>
+        <v>-0.09250707423188109</v>
       </c>
     </row>
     <row r="6">
@@ -5599,34 +5596,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>43521</v>
+        <v>41117</v>
       </c>
       <c r="M6" t="n">
-        <v>105</v>
+        <v>1210</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1526629324515709</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1526629324515709</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="P6" t="n">
-        <v>104</v>
+        <v>1209</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.05081259100693263</v>
+        <v>0.1828975982396791</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.02780498354473863</v>
+        <v>0.1211945088828175</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -5636,61 +5633,61 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1526629324515709</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1526629324515709</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>41</v>
+        <v>855</v>
       </c>
       <c r="AC6" t="n">
-        <v>-35</v>
+        <v>-5</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1801678910297944</v>
+        <v>0.798509113087996</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>3.89908139934031e-06</v>
+        <v>-0.03205175018886679</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>7.319584456988437e-06</v>
+        <v>0.08751977085293516</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.0003591061024440095</v>
+        <v>0.004555847738083332</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.01471828495760386</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-15</v>
+        <v>256</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.1461547765376521</v>
+        <v>0.1280357344784944</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>0.01697417431465009</v>
+        <v>-0.003416596729815757</v>
       </c>
     </row>
     <row r="7">
@@ -5736,34 +5733,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>43773</v>
+        <v>40133</v>
       </c>
       <c r="M7" t="n">
-        <v>281</v>
+        <v>531</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.314556771252366</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.314556771252366</v>
       </c>
       <c r="P7" t="n">
-        <v>280</v>
+        <v>530</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.07217823081495067</v>
+        <v>0.1125096100387912</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.06442125125312613</v>
+        <v>0.04941380586286755</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -5773,40 +5770,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.314556771252366</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.314556771252366</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="AC7" t="n">
-        <v>141</v>
+        <v>-684</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.1801780858076512</v>
+        <v>0.4589100279349019</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.03662016678978684</v>
+        <v>-0.1038324532088168</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0</v>
+        <v>0.2169469123186846</v>
       </c>
       <c r="AH7" t="n">
-        <v>176</v>
+        <v>-691</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -5865,34 +5862,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>43558</v>
+        <v>41158</v>
       </c>
       <c r="M8" t="n">
-        <v>132</v>
+        <v>1238</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.4784516009673341</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.4784516009673341</v>
       </c>
       <c r="P8" t="n">
-        <v>131</v>
+        <v>1237</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.0510992095335791</v>
+        <v>0.1962136257024649</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.031321198467107</v>
+        <v>0.131512697301539</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -5902,52 +5899,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.4784516009673341</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.4784516009673341</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>68</v>
+        <v>883</v>
       </c>
       <c r="AC8" t="n">
-        <v>-8</v>
+        <v>23</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1801780858076512</v>
+        <v>0.9173675959023841</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.00352011400376771</v>
+        <v>-0.02173356177014529</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
+        <v>0.05305208260371652</v>
       </c>
       <c r="AH8" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.003875321024812379</v>
+        <v>0.01487403615680483</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.01472560454206084</v>
+        <v>-0.03446768824921864</v>
       </c>
       <c r="AL8" t="n">
-        <v>12</v>
+        <v>284</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -5998,34 +5995,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43458</v>
+        <v>40911</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43773</v>
+        <v>41366</v>
       </c>
       <c r="M9" t="n">
-        <v>281</v>
+        <v>1378</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.1735482952034543</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.2236726154223472</v>
       </c>
       <c r="P9" t="n">
-        <v>280</v>
+        <v>1242</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.07217823081495067</v>
+        <v>0.1100632696760414</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.06442125125312613</v>
+        <v>0.07782648434749258</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -6035,40 +6032,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>64</v>
+        <v>1067</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>712</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.1735482952034543</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.2236726154223472</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>217</v>
+        <v>311</v>
       </c>
       <c r="AC9" t="n">
-        <v>141</v>
+        <v>-549</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1801780858076512</v>
+        <v>0.2099920590594921</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.03662016678978684</v>
+        <v>-0.07541977472419174</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0</v>
+        <v>0.3579553883675963</v>
       </c>
       <c r="AH9" t="n">
-        <v>176</v>
+        <v>-556</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -6127,34 +6124,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>43558</v>
+        <v>41117</v>
       </c>
       <c r="M10" t="n">
-        <v>132</v>
+        <v>1210</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.4594211534155789</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.4594211534155789</v>
       </c>
       <c r="P10" t="n">
-        <v>131</v>
+        <v>1209</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.0510992095335791</v>
+        <v>0.2055360906551242</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.031321198467107</v>
+        <v>0.1361955859693619</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -6164,52 +6161,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.4594211534155789</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.4594211534155789</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>68</v>
+        <v>855</v>
       </c>
       <c r="AC10" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.1801780858076512</v>
+        <v>0.8498689068548893</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.00352011400376771</v>
+        <v>-0.01705067310232239</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0</v>
+        <v>0.07208253015547172</v>
       </c>
       <c r="AH10" t="n">
-        <v>27</v>
+        <v>-12</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.003875321024812379</v>
+        <v>0.01955692482462773</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.01472560454206084</v>
+        <v>-0.01543724069746344</v>
       </c>
       <c r="AL10" t="n">
-        <v>12</v>
+        <v>256</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -6512,34 +6509,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="M2" t="n">
+        <v>143</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.1989728318606708</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2022979914860072</v>
+      </c>
+      <c r="P2" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.08183226369428324</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05211846719049073</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="M2" t="n">
-        <v>78</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="P2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1403286526425155</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.05728893254440421</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -6549,22 +6546,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606708</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -6573,7 +6570,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4088864968986545</v>
+        <v>0.2483971078320053</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -6621,34 +6618,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>43521</v>
+      </c>
+      <c r="M3" t="n">
+        <v>106</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.154217499687799</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.154217499687799</v>
+      </c>
+      <c r="P3" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.05190748421809096</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.02849756106243677</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>44053</v>
-      </c>
-      <c r="M3" t="n">
-        <v>120</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="P3" t="n">
-        <v>119</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1276281687846577</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.06448371536726236</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -6658,31 +6655,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="AC3" t="n">
-        <v>42</v>
+        <v>-37</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4427931145010366</v>
+        <v>0.1823370661261887</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -6738,34 +6735,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>43539</v>
+      </c>
+      <c r="M4" t="n">
+        <v>120</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1373591481699221</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1410541034597296</v>
+      </c>
+      <c r="P4" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.04694462358448135</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.0274071811141844</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M4" t="n">
-        <v>122</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P4" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1167974844615735</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.05949724743333182</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -6775,40 +6772,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1373591481699221</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="AC4" t="n">
-        <v>44</v>
+        <v>-23</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1592309799362237</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.004986467933930532</v>
+        <v>-0.001090379948252361</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.01665345881679148</v>
+        <v>0.01685835151787685</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -6863,83 +6860,91 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>43511</v>
+      </c>
+      <c r="M5" t="n">
+        <v>101</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1476161445200224</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1513122874756199</v>
+      </c>
+      <c r="P5" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.05058119699294059</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.02711284004857402</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>473</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="P5" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.2421098170484373</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.2421098170484373</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>1</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>-0.2448984336711736</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.1476161445200224</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.1513122874756199</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-42</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4427931145010366</v>
+        <v>0.1731803618416725</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.177626101681175</v>
+        <v>-0.001384721013862746</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>0.006601355167776601</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-5</v>
+      </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.1482515156944797</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.1210794689914346</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6988,34 +6993,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>43521</v>
+      </c>
+      <c r="M6" t="n">
+        <v>106</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1520874296386187</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.152662932451571</v>
+      </c>
+      <c r="P6" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.05057459161419035</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.02776579397833505</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>44069</v>
-      </c>
-      <c r="M6" t="n">
-        <v>132</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="P6" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1332253563260969</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.07057055616780003</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -7025,58 +7030,62 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.1520874296386187</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.152662932451571</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="AC6" t="n">
-        <v>54</v>
+        <v>-37</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4427931145010366</v>
+        <v>0.179366876910197</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.006086840800537674</v>
+        <v>-0.0007317670841017164</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
+        <v>0.00213007004918031</v>
       </c>
       <c r="AH6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.01107330873446821</v>
+        <v>0.0003586128641506446</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.01665345881679148</v>
+        <v>-0.01472828146869654</v>
       </c>
       <c r="AL6" t="n">
-        <v>10</v>
+        <v>-14</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="n">
+        <v>0.1482515156944797</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>0.01442816182558482</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7121,34 +7130,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>43773</v>
+      </c>
+      <c r="M7" t="n">
+        <v>282</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.154217499687799</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.154217499687799</v>
+      </c>
+      <c r="P7" t="n">
+        <v>281</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.07358763972198773</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.06570280555928902</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>44372</v>
-      </c>
-      <c r="M7" t="n">
-        <v>341</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="P7" t="n">
-        <v>340</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1886246930897304</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.1602221032043226</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -7158,40 +7167,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>318</v>
+        <v>217</v>
       </c>
       <c r="AC7" t="n">
-        <v>263</v>
+        <v>139</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4427931145010366</v>
+        <v>0.1823370661261887</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.09573838783706029</v>
+        <v>0.03720524449685225</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>221</v>
+        <v>176</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -7250,34 +7259,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="M8" t="n">
+        <v>134</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.154217499687799</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.154217499687799</v>
+      </c>
+      <c r="P8" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.05210680649302959</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.03213269596277261</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>44069</v>
-      </c>
-      <c r="M8" t="n">
-        <v>132</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="P8" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1332253563260969</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.07057055616780003</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -7287,52 +7296,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="AC8" t="n">
-        <v>54</v>
+        <v>-9</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4427931145010366</v>
+        <v>0.1823370661261887</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.006086840800537674</v>
+        <v>0.003635134900335849</v>
       </c>
       <c r="AG8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.01107330873446821</v>
+        <v>0.00472551484858821</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.01665345881679148</v>
+        <v>-0.01685835151787685</v>
       </c>
       <c r="AL8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -7383,76 +7392,80 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>43773</v>
+      </c>
+      <c r="M9" t="n">
+        <v>282</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.154217499687799</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.154217499687799</v>
+      </c>
+      <c r="P9" t="n">
+        <v>281</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.07358763972198773</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.06570280555928902</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>473</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.3068999359996033</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.3068999359996033</v>
-      </c>
-      <c r="P9" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.2109796098651114</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.2109796098651114</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.1682619534377185</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.3068999359996033</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3068999359996033</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>217</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>139</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.4427931145010364</v>
+        <v>0.1823370661261887</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.1464958944978491</v>
+        <v>0.03720524449685225</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>1.110223024625157e-16</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>176</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -7508,34 +7521,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="M10" t="n">
+        <v>134</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.154217499687799</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.154217499687799</v>
+      </c>
+      <c r="P10" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.05210680649302959</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.03213269596277261</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>44069</v>
-      </c>
-      <c r="M10" t="n">
-        <v>132</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="P10" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1332253563260969</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.07057055616780003</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -7545,52 +7558,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="AC10" t="n">
-        <v>54</v>
+        <v>-9</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.4427931145010366</v>
+        <v>0.1823370661261887</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.006086840800537674</v>
+        <v>0.003635134900335849</v>
       </c>
       <c r="AG10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.01107330873446821</v>
+        <v>0.00472551484858821</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.01665345881679148</v>
+        <v>-0.01685835151787685</v>
       </c>
       <c r="AL10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -7893,34 +7906,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="M2" t="n">
+        <v>78</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="P2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1403286526425155</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05728893254440421</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="M2" t="n">
-        <v>473</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.3239608533428744</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.3239608533428744</v>
-      </c>
-      <c r="P2" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1873955345996986</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1456175032694572</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -7930,22 +7943,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -7954,7 +7967,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4792042812088533</v>
+        <v>0.4088864968986545</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -8002,34 +8015,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>44053</v>
+      </c>
+      <c r="M3" t="n">
+        <v>120</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3068999359996034</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3068999359996034</v>
+      </c>
+      <c r="P3" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1276281687846577</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.06448371536726236</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>44874</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45092</v>
-      </c>
-      <c r="M3" t="n">
-        <v>364</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.3457775114458427</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.3457775114458427</v>
-      </c>
-      <c r="P3" t="n">
-        <v>363</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.2151703805871633</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.14672161268614</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -8039,31 +8052,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3457775114458427</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3457775114458427</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>149</v>
+        <v>97</v>
       </c>
       <c r="AC3" t="n">
-        <v>-71</v>
+        <v>42</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.5285319864347935</v>
+        <v>0.4427931145010366</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -8119,34 +8132,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M4" t="n">
+        <v>122</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="P4" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1167974844615735</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.05949724743333182</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45131</v>
-      </c>
-      <c r="M4" t="n">
-        <v>389</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2376608476183659</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2376608476183659</v>
-      </c>
-      <c r="P4" t="n">
-        <v>388</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1306673287628706</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.09210103019783453</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -8156,40 +8169,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="AC4" t="n">
-        <v>-26</v>
+        <v>44</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.3117521209239831</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.05462058248830545</v>
+        <v>-0.004986467933930532</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.1081166638274768</v>
+        <v>0.01665345881679148</v>
       </c>
       <c r="AH4" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8244,91 +8257,83 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>473</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.3068999359996034</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.3068999359996034</v>
+      </c>
+      <c r="P5" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.2421098170484373</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.2421098170484373</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>45226</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>45455</v>
-      </c>
-      <c r="M5" t="n">
-        <v>613</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.3010232303180663</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.312323466053521</v>
-      </c>
-      <c r="P5" t="n">
-        <v>550</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.2131882439505981</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.1885439535444547</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>-0.2448984336711736</v>
+      </c>
       <c r="W5" t="n">
-        <v>457</v>
+        <v>23</v>
       </c>
       <c r="X5" t="n">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3010232303180663</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.312323466053521</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>156</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-64</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4306627106578171</v>
+        <v>0.4427931145010366</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.04182234085831468</v>
+        <v>0.177626101681175</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.04475428112777635</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.8786786156143458</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.4669938870301228</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8377,34 +8382,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="M6" t="n">
+        <v>132</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3068999359996034</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3068999359996034</v>
+      </c>
+      <c r="P6" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1332253563260969</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.07057055616780003</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>44874</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45352</v>
-      </c>
-      <c r="M6" t="n">
-        <v>542</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.3207476547189958</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.3207476547189958</v>
-      </c>
-      <c r="P6" t="n">
-        <v>541</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.2041050392798871</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.1697535298856395</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -8414,62 +8419,58 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3207476547189958</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3207476547189958</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>327</v>
+        <v>109</v>
       </c>
       <c r="AC6" t="n">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4722069153641326</v>
+        <v>0.4427931145010366</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.02303191719949949</v>
+        <v>0.006086840800537674</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.02502985672684688</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>178</v>
+        <v>12</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.07765249968780494</v>
+        <v>0.01107330873446821</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.08308680710062988</v>
+        <v>-0.01665345881679148</v>
       </c>
       <c r="AL6" t="n">
-        <v>133</v>
+        <v>10</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.8786786156143458</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.1063115227943896</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8514,34 +8515,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>44372</v>
+      </c>
+      <c r="M7" t="n">
+        <v>341</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.3068999359996034</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.3068999359996034</v>
+      </c>
+      <c r="P7" t="n">
+        <v>340</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1886246930897304</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.1602221032043226</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44628</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45063</v>
-      </c>
-      <c r="M7" t="n">
-        <v>344</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.1789082384476008</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.1789082384476008</v>
-      </c>
-      <c r="P7" t="n">
-        <v>343</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.07180996464459063</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.04760575224407835</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -8551,40 +8552,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="X7" t="n">
-        <v>-151</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1789082384476008</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1789082384476008</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="AC7" t="n">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2178906753483283</v>
+        <v>0.4427931145010366</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.09911586044206164</v>
+        <v>0.09573838783706029</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1668692729982418</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -8643,34 +8644,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="M8" t="n">
+        <v>132</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.3068999359996034</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.3068999359996034</v>
+      </c>
+      <c r="P8" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1332253563260969</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.07057055616780003</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45092</v>
-      </c>
-      <c r="M8" t="n">
-        <v>364</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.2667855627451129</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.2667855627451129</v>
-      </c>
-      <c r="P8" t="n">
-        <v>363</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1647132131692218</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.1123155900963533</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -8680,52 +8681,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.2667855627451129</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.2667855627451129</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="AC8" t="n">
-        <v>-51</v>
+        <v>54</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.3638574872365345</v>
+        <v>0.4427931145010366</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.03440602258978664</v>
+        <v>0.006086840800537674</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.07899194870072979</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.02021455989851881</v>
+        <v>0.01107330873446821</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.02912471512674697</v>
+        <v>-0.01665345881679148</v>
       </c>
       <c r="AL8" t="n">
-        <v>-25</v>
+        <v>10</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -8776,91 +8777,83 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>473</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.3068999359996033</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.3068999359996033</v>
+      </c>
+      <c r="P9" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.2109796098651114</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.2109796098651114</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>45226</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>45231</v>
-      </c>
-      <c r="M9" t="n">
-        <v>460</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.01678726098360461</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.104492178039316</v>
-      </c>
-      <c r="P9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.01650716285804225</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.01264992848657863</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>-0.1682619534377185</v>
+      </c>
       <c r="W9" t="n">
-        <v>457</v>
+        <v>23</v>
       </c>
       <c r="X9" t="n">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.01678726098360461</v>
+        <v>-0.3068999359996033</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.104492178039316</v>
+        <v>-0.3068999359996033</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-217</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.01707388474278582</v>
+        <v>0.4427931145010364</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1340716841995613</v>
+        <v>0.1464958944978491</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.3289902504622381</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-146</v>
-      </c>
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="n">
-        <v>0.1128423029659751</v>
-      </c>
-      <c r="AO9" s="3" t="n">
-        <v>-0.1012753618169033</v>
-      </c>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8909,34 +8902,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="M10" t="n">
+        <v>132</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.3068999359996034</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.3068999359996034</v>
+      </c>
+      <c r="P10" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.1332253563260969</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.07057055616780003</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45125</v>
-      </c>
-      <c r="M10" t="n">
-        <v>385</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2376608476183659</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2376608476183659</v>
-      </c>
-      <c r="P10" t="n">
-        <v>384</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1313200072888495</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09208517592225469</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -8946,62 +8939,58 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>190</v>
+        <v>109</v>
       </c>
       <c r="AC10" t="n">
-        <v>-30</v>
+        <v>54</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.3117521209239831</v>
+        <v>0.4427931145010366</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.05463643676388528</v>
+        <v>0.006086840800537674</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.1081166638274768</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>-1.585427557983243e-05</v>
+        <v>0.01107330873446821</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>0</v>
+        <v>-0.01665345881679148</v>
       </c>
       <c r="AL10" t="n">
-        <v>-4</v>
+        <v>10</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.1128423029659751</v>
-      </c>
-      <c r="AO10" s="3" t="n">
-        <v>-0.01183659930796777</v>
-      </c>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9298,34 +9287,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="M2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.3239608533428744</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.3239608533428744</v>
+      </c>
+      <c r="P2" t="n">
+        <v>472</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1873955345996986</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.1456175032694572</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45835</v>
-      </c>
-      <c r="M2" t="n">
-        <v>89</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="P2" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1032426212645815</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.06633642004451831</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -9335,22 +9324,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428744</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428744</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -9359,7 +9348,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2889940469367012</v>
+        <v>0.4792042812088533</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -9407,34 +9396,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>44874</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45092</v>
+      </c>
+      <c r="M3" t="n">
+        <v>364</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3457775114458427</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3457775114458427</v>
+      </c>
+      <c r="P3" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.2151703805871633</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.14672161268614</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45884</v>
-      </c>
-      <c r="M3" t="n">
-        <v>123</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.1856244724967976</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.1856244724967976</v>
-      </c>
-      <c r="P3" t="n">
-        <v>122</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.08596294066132025</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.06483266282103413</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -9444,31 +9433,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>34</v>
+        <v>215</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1856244724967976</v>
+        <v>-0.3457775114458427</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1856244724967976</v>
+        <v>-0.3457775114458427</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="AC3" t="n">
-        <v>34</v>
+        <v>-71</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2279347380021408</v>
+        <v>0.5285319864347935</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -9524,34 +9513,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45131</v>
+      </c>
+      <c r="M4" t="n">
+        <v>389</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="P4" t="n">
+        <v>388</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1306673287628706</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.09210103019783453</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="M4" t="n">
-        <v>136</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="P4" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.06348808787815403</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.05032969331821049</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -9561,40 +9550,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>102</v>
+        <v>194</v>
       </c>
       <c r="AC4" t="n">
-        <v>47</v>
+        <v>-26</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1822068127687015</v>
+        <v>0.3117521209239831</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.01450296950282364</v>
+        <v>-0.05462058248830545</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.03150015955871077</v>
+        <v>0.1081166638274768</v>
       </c>
       <c r="AH4" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -9649,73 +9638,77 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45455</v>
+      </c>
+      <c r="M5" t="n">
+        <v>613</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.3010232303180663</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.312323466053521</v>
+      </c>
+      <c r="P5" t="n">
+        <v>550</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.2131882439505981</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.1885439535444547</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>88</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="X5" t="n">
-        <v>-34</v>
+        <v>262</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0.3010232303180663</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0.312323466053521</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="AC5" t="n">
-        <v>-55</v>
+        <v>-64</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0</v>
+        <v>0.4306627106578171</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.06483266282103413</v>
+        <v>0.04182234085831468</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.1856244724967976</v>
+        <v>0.04475428112777635</v>
       </c>
       <c r="AH5" t="n">
-        <v>-89</v>
+        <v>7</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -9725,10 +9718,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.1659072706450004</v>
+        <v>0.8786786156143458</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.1282572424698077</v>
+        <v>-0.4669938870301228</v>
       </c>
     </row>
     <row r="6">
@@ -9778,34 +9771,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>44874</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45352</v>
+      </c>
+      <c r="M6" t="n">
+        <v>542</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3207476547189958</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3207476547189958</v>
+      </c>
+      <c r="P6" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.2041050392798871</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.1697535298856395</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="M6" t="n">
-        <v>136</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="P6" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.06348808787815403</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.05032969331821049</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -9815,61 +9808,61 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>34</v>
+        <v>215</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.3207476547189958</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.3207476547189958</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>102</v>
+        <v>327</v>
       </c>
       <c r="AC6" t="n">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1822068127687015</v>
+        <v>0.4722069153641326</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.01450296950282364</v>
+        <v>0.02303191719949949</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.03150015955871077</v>
+        <v>0.02502985672684688</v>
       </c>
       <c r="AH6" t="n">
-        <v>13</v>
+        <v>178</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0</v>
+        <v>0.07765249968780494</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>0</v>
+        <v>-0.08308680710062988</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.1659072706450004</v>
+        <v>0.8786786156143458</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>-0.04877167935164584</v>
+        <v>-0.1063115227943896</v>
       </c>
     </row>
     <row r="7">
@@ -9915,73 +9908,77 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>44628</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45063</v>
+      </c>
+      <c r="M7" t="n">
+        <v>344</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1789082384476008</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1789082384476008</v>
+      </c>
+      <c r="P7" t="n">
+        <v>343</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.07180996464459063</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.04760575224407835</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" t="n">
-        <v>88</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="X7" t="n">
-        <v>-34</v>
+        <v>-151</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0</v>
+        <v>-0.1789082384476008</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0</v>
+        <v>-0.1789082384476008</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AC7" t="n">
-        <v>-55</v>
+        <v>80</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0</v>
+        <v>0.2178906753483283</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.06483266282103413</v>
+        <v>-0.09911586044206164</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1856244724967976</v>
+        <v>0.1668692729982418</v>
       </c>
       <c r="AH7" t="n">
-        <v>-89</v>
+        <v>151</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -9990,12 +9987,8 @@
       <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" s="3" t="n">
-        <v>0.03966424779839195</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>-0.03329611901649576</v>
-      </c>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10044,34 +10037,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45092</v>
+      </c>
+      <c r="M8" t="n">
+        <v>364</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.2667855627451129</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.2667855627451129</v>
+      </c>
+      <c r="P8" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1647132131692218</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.1123155900963533</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45883</v>
-      </c>
-      <c r="M8" t="n">
-        <v>122</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="P8" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.06502239195636811</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.04884130400914963</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -10081,62 +10074,58 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2667855627451129</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2667855627451129</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="AC8" t="n">
-        <v>33</v>
+        <v>-51</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1822068127687015</v>
+        <v>0.3638574872365345</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.0159913588118845</v>
+        <v>-0.03440602258978664</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.03150015955871077</v>
+        <v>0.07899194870072979</v>
       </c>
       <c r="AH8" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>-0.00148838930906086</v>
+        <v>0.02021455989851881</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>0</v>
+        <v>-0.02912471512674697</v>
       </c>
       <c r="AL8" t="n">
-        <v>-14</v>
+        <v>-25</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
       </c>
-      <c r="AN8" s="3" t="n">
-        <v>0.03966424779839195</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>0.02521277934010779</v>
-      </c>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10181,73 +10170,77 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="M9" t="n">
+        <v>460</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.01678726098360461</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.104492178039316</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.01650716285804225</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.01264992848657863</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>88</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="X9" t="n">
-        <v>-34</v>
+        <v>262</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>-0.01678726098360461</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>0</v>
+        <v>-0.104492178039316</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC9" t="n">
-        <v>-55</v>
+        <v>-217</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0</v>
+        <v>0.01707388474278582</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.06483266282103413</v>
+        <v>-0.1340716841995613</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.1856244724967976</v>
+        <v>0.3289902504622381</v>
       </c>
       <c r="AH9" t="n">
-        <v>-89</v>
+        <v>-146</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -10257,10 +10250,10 @@
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="n">
-        <v>0.1659072706450004</v>
+        <v>0.1128423029659751</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.1282572424698077</v>
+        <v>-0.1012753618169033</v>
       </c>
     </row>
     <row r="10">
@@ -10310,34 +10303,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45125</v>
+      </c>
+      <c r="M10" t="n">
+        <v>385</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="P10" t="n">
+        <v>384</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.1313200072888495</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.09208517592225469</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45883</v>
-      </c>
-      <c r="M10" t="n">
-        <v>122</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="P10" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.06502239195636811</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.04884130400914963</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -10347,61 +10340,61 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>88</v>
+        <v>190</v>
       </c>
       <c r="AC10" t="n">
-        <v>33</v>
+        <v>-30</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.1822068127687015</v>
+        <v>0.3117521209239831</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.0159913588118845</v>
+        <v>-0.05463643676388528</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.03150015955871077</v>
+        <v>0.1081166638274768</v>
       </c>
       <c r="AH10" t="n">
-        <v>-1</v>
+        <v>41</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>-0.00148838930906086</v>
+        <v>-1.585427557983243e-05</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>0.1659072706450004</v>
+        <v>0.1128423029659751</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>-0.04877167935164584</v>
+        <v>-0.01183659930796777</v>
       </c>
     </row>
   </sheetData>
@@ -10415,7 +10408,1408 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AO10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base_ulcer</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base_depth</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_days</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_censored</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb_ulcer</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb_depth</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_days</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_censored</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="M2" t="n">
+        <v>89</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="P2" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.06633642004451831</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.2889940469367012</v>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="M3" t="n">
+        <v>123</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1856244724967976</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1856244724967976</v>
+      </c>
+      <c r="P3" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.08596294066132025</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.06483266282103413</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>34</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>-0.1856244724967976</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>-0.1856244724967976</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>89</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0.2279347380021408</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="M4" t="n">
+        <v>136</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="P4" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.06348808787815403</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.05032969331821049</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>34</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>102</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>47</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>0.1822068127687015</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>-0.01450296950282364</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>0.03150015955871077</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>89</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T5" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>-0.06483266282103413</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>0.1856244724967976</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-89</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.1659072706450004</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.1282572424698077</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="M6" t="n">
+        <v>136</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="P6" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.06348808787815403</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.05032969331821049</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>34</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>102</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>47</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>0.1822068127687015</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>-0.01450296950282364</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>0.03150015955871077</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="3" t="n">
+        <v>0.1659072706450004</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>-0.04877167935164584</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>89</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T7" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>-0.06483266282103413</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0.1856244724967976</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-89</v>
+      </c>
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" s="3" t="n">
+        <v>0.03966424779839195</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>-0.03329611901649576</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="M8" t="n">
+        <v>122</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="P8" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.06502239195636811</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.04884130400914963</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>34</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>88</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>33</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0.1822068127687015</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>-0.0159913588118845</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0.03150015955871077</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3" t="n">
+        <v>-0.00148838930906086</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AM8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="3" t="n">
+        <v>0.03966424779839195</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>0.02521277934010779</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>89</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T9" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>-0.06483266282103413</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>0.1856244724967976</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-89</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.1659072706450004</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.1282572424698077</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="M10" t="n">
+        <v>122</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="P10" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.06502239195636811</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.04884130400914963</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>34</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="AA10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>88</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>33</v>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="3" t="n">
+        <v>0.1822068127687015</v>
+      </c>
+      <c r="AF10" s="3" t="n">
+        <v>-0.0159913588118845</v>
+      </c>
+      <c r="AG10" s="3" t="n">
+        <v>0.03150015955871077</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="3" t="n">
+        <v>-0.00148838930906086</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AM10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="3" t="n">
+        <v>0.1659072706450004</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>-0.04877167935164584</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10521,24 +11915,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>23</v>
+      </c>
       <c r="J2" s="3" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -10569,20 +11961,20 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-131</v>
+        <v>196</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="3" t="n">
-        <v>0.7281976744186046</v>
+        <v>0.473655019412091</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -10616,23 +12008,23 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-120</v>
+        <v>-131</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-57</v>
+        <v>523</v>
       </c>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="3" t="n">
-        <v>0.04137931034482759</v>
+        <v>0.7281976744186046</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -10662,19 +12054,21 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="n">
+        <v>-119</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>-57</v>
+      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.04794520547945205</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -10707,24 +12101,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>-132</v>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>0.3625730994152047</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -10755,21 +12147,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>-132</v>
+      </c>
       <c r="G7" t="n">
-        <v>94</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>1</v>
+        <v>0.3625730994152047</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -10786,37 +12180,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>259</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>59</v>
-      </c>
+        <v>-94</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" s="3" t="n">
-        <v>0.1058171745152355</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -10843,27 +12235,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>23</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>0.3204941860465116</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -10890,25 +12280,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>59</v>
+      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
+        <v>0.1059345535219079</v>
+      </c>
+      <c r="K10" t="n">
         <v>6</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0.4206896551724138</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -10935,25 +12327,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3204941860465116</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -10980,24 +12374,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>119</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -11027,27 +12419,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>58</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
       <c r="J13" s="3" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -11064,24 +12454,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -11091,10 +12481,10 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>0.313573407202216</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -11111,37 +12501,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>59</v>
+        <v>-30</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>0.4585755813953488</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -11168,25 +12558,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.4206896551724138</v>
-      </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -11213,25 +12605,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>183</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3139212423738214</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -11258,27 +12652,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-63</v>
+        <v>59</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="G18" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.7309941520467836</v>
+        <v>0.4585755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -11305,32 +12699,169 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>58</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="3" t="n">
-        <v>1</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-63</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="G21" t="n">
+        <v>63</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
+        <v>0.7309941520467836</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-94</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="G22" t="n">
+        <v>94</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
